--- a/samples/karoo-coffee-books-q3-2026.xlsx
+++ b/samples/karoo-coffee-books-q3-2026.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="130">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -206,15 +206,24 @@
     <t xml:space="preserve">Ledger account</t>
   </si>
   <si>
+    <t xml:space="preserve">VAT claimable</t>
+  </si>
+  <si>
     <t xml:space="preserve">6100</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes (commercial rent)</t>
+  </si>
+  <si>
     <t xml:space="preserve">6200</t>
   </si>
   <si>
     <t xml:space="preserve">Electricity &amp; Water</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">6300</t>
   </si>
   <si>
@@ -227,10 +236,22 @@
     <t xml:space="preserve">Fuel &amp; Travel</t>
   </si>
   <si>
+    <t xml:space="preserve">No (fuel is zero-rated in SA)</t>
+  </si>
+  <si>
     <t xml:space="preserve">6800</t>
   </si>
   <si>
     <t xml:space="preserve">Marketing &amp; Advertising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Supplies</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
@@ -1151,12 +1172,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1169,16 +1191,22 @@
       <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1186,10 +1214,13 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1197,10 +1228,13 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1208,10 +1242,13 @@
         <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1219,10 +1256,27 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1252,86 +1306,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1371,40 +1425,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,13 +1466,13 @@
         <v>46206</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>40</v>
@@ -1447,7 +1501,7 @@
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1455,13 +1509,13 @@
         <v>46213</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>25</v>
@@ -1489,7 +1543,7 @@
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1497,13 +1551,13 @@
         <v>46238</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>60</v>
@@ -1534,7 +1588,7 @@
         <v>5</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1542,13 +1596,13 @@
         <v>46267</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>40</v>
@@ -1572,7 +1626,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1580,13 +1634,13 @@
         <v>46275</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>1</v>
@@ -1615,7 +1669,7 @@
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1653,34 +1707,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1688,13 +1742,13 @@
         <v>46204</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>5</v>
@@ -1718,7 +1772,7 @@
         <v>46218</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1726,13 +1780,13 @@
         <v>46235</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>4</v>
@@ -1756,7 +1810,7 @@
         <v>46254</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1764,13 +1818,13 @@
         <v>46242</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>2000</v>
@@ -1792,7 +1846,7 @@
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1825,16 +1879,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1842,14 +1896,14 @@
         <v>46234</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="n">
         <v>185</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1857,14 +1911,14 @@
         <v>46265</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="n">
         <v>185</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1872,14 +1926,14 @@
         <v>46277</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>500</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,14 +1941,14 @@
         <v>46295</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="n">
         <v>185</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
